--- a/MinMax/scripts/comparison/violations_comparison_table_57_1000.xlsx
+++ b/MinMax/scripts/comparison/violations_comparison_table_57_1000.xlsx
@@ -459,16 +459,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>2.238739580207039E-05</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0001244548766408116</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0.1159230321645737</v>
+        <v>0.1162268295884132</v>
       </c>
       <c r="E2">
-        <v>0.04440952092409134</v>
+        <v>0.04612599313259125</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -476,16 +476,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.02505838871002197</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.06854522228240967</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0.730965793132782</v>
       </c>
       <c r="E3">
-        <v>0.2687543630599976</v>
+        <v>0.2808365821838379</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -493,16 +493,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.0005042819539085031</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0009509971714578569</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0.006043176166713238</v>
+        <v>0.006212846841663122</v>
       </c>
       <c r="E4">
-        <v>0.0843450129032135</v>
+        <v>0.08610174804925919</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -510,16 +510,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.06382539868354797</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.1100349575281143</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0.1377009749412537</v>
+        <v>0.1436015367507935</v>
       </c>
       <c r="E5">
-        <v>0.8876372575759888</v>
+        <v>0.9570861458778381</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -533,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.01016720850020647</v>
+        <v>0.01093324925750494</v>
       </c>
       <c r="E6">
-        <v>0.06669703125953674</v>
+        <v>0.06887058913707733</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -553,7 +553,7 @@
         <v>0.2990880012512207</v>
       </c>
       <c r="E7">
-        <v>0.7871901988983154</v>
+        <v>0.8703179359436035</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -629,10 +629,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>5.036476795794442E-05</v>
+        <v>5.034722198615782E-05</v>
       </c>
       <c r="C12">
-        <v>5.036439324612729E-05</v>
+        <v>5.034682180848904E-05</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -646,10 +646,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.002880990505218506</v>
+        <v>0.00288158655166626</v>
       </c>
       <c r="C13">
-        <v>0.002880394458770752</v>
+        <v>0.002881228923797607</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>1.563908674400405E-08</v>
+        <v>1.644095058699641E-08</v>
       </c>
       <c r="C16">
-        <v>1.550178168802081E-08</v>
+        <v>1.665817633195007E-08</v>
       </c>
       <c r="D16">
-        <v>1.119286353387283E-06</v>
+        <v>1.119903117796639E-06</v>
       </c>
       <c r="E16">
-        <v>1.116991671642425E-06</v>
+        <v>1.116221142183349E-06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -714,16 +714,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>4.316697649709941E-07</v>
+        <v>4.490620972875756E-07</v>
       </c>
       <c r="C17">
-        <v>4.462335527246028E-07</v>
+        <v>4.654903360545461E-07</v>
       </c>
       <c r="D17">
-        <v>9.940071588823129E-06</v>
+        <v>9.94007132248953E-06</v>
       </c>
       <c r="E17">
-        <v>1.023592640284846E-05</v>
+        <v>1.023592631099746E-05</v>
       </c>
     </row>
   </sheetData>
